--- a/data/trans_orig/IP31C_R_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP31C_R_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,107 +720,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9159</t>
+          <t>4420</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>1601</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16319</t>
+          <t>9483</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>11112</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>5726</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8673</t>
+          <t>20229</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>12459</t>
+          <t>15532</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7190</t>
+          <t>9161</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20269</t>
+          <t>23611</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -833,107 +833,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>158</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>105092</t>
+          <t>118058</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97932</t>
+          <t>112995</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>109318</t>
+          <t>120877</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>176</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>132985</t>
+          <t>107486</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>127612</t>
+          <t>98369</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>135355</t>
+          <t>112872</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>334</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>238077</t>
+          <t>225544</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>230267</t>
+          <t>217465</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>243346</t>
+          <t>231915</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>96,2%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122478</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122478</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122478</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136285</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136285</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136285</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>250536</t>
+          <t>241076</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>250536</t>
+          <t>241076</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>250536</t>
+          <t>241076</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,107 +1063,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14386</t>
+          <t>34682</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8795</t>
+          <t>26210</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21066</t>
+          <t>46382</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28510</t>
+          <t>16832</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19940</t>
+          <t>10825</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39211</t>
+          <t>24835</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>64</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>42896</t>
+          <t>51515</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32212</t>
+          <t>40146</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55041</t>
+          <t>65178</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -1176,107 +1176,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>280</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>170824</t>
+          <t>195225</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>164144</t>
+          <t>183525</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>176415</t>
+          <t>203697</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>245</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>217617</t>
+          <t>162981</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>206916</t>
+          <t>154978</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>226187</t>
+          <t>168988</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>525</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>388441</t>
+          <t>358205</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>376296</t>
+          <t>344542</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>399125</t>
+          <t>369574</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>90,2%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>229907</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>229907</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>229907</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>267</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>185210</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>185210</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>185210</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>246127</t>
+          <t>179813</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>246127</t>
+          <t>179813</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>246127</t>
+          <t>179813</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>431337</t>
+          <t>409720</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>431337</t>
+          <t>409720</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>431337</t>
+          <t>409720</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,107 +1406,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>14466</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2460</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11524</t>
+          <t>22334</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14970</t>
+          <t>10713</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9069</t>
+          <t>5415</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22785</t>
+          <t>20178</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>21220</t>
+          <t>25178</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13612</t>
+          <t>17136</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31483</t>
+          <t>36194</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>11,28%</t>
         </is>
       </c>
     </row>
@@ -1519,107 +1519,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>200</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>181330</t>
+          <t>152056</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>176056</t>
+          <t>144188</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>185120</t>
+          <t>157599</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>210</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>168119</t>
+          <t>143678</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>160304</t>
+          <t>134213</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>174020</t>
+          <t>148976</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>410</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>349450</t>
+          <t>295734</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>339187</t>
+          <t>284718</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>357058</t>
+          <t>303776</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>94,66%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>187580</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>187580</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>187580</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>154391</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>154391</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>154391</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>370670</t>
+          <t>320912</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>370670</t>
+          <t>320912</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>370670</t>
+          <t>320912</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,107 +1749,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18245</t>
+          <t>19749</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12505</t>
+          <t>13226</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26804</t>
+          <t>27897</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18484</t>
+          <t>20871</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12259</t>
+          <t>14058</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27842</t>
+          <t>29065</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>54</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>36728</t>
+          <t>40620</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27786</t>
+          <t>30833</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46912</t>
+          <t>50635</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -1862,107 +1862,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>204</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>145727</t>
+          <t>146416</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>137168</t>
+          <t>138268</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>151467</t>
+          <t>152939</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>208</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>158825</t>
+          <t>142641</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>149467</t>
+          <t>134447</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>165050</t>
+          <t>149454</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>412</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>304553</t>
+          <t>289057</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>294369</t>
+          <t>279042</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>313495</t>
+          <t>298844</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>90,65%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>163972</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>163972</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>163972</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163512</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163512</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163512</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>341281</t>
+          <t>329677</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>341281</t>
+          <t>329677</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>341281</t>
+          <t>329677</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,107 +2092,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>48040</t>
+          <t>73317</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36228</t>
+          <t>60289</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61083</t>
+          <t>90234</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>72</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>65264</t>
+          <t>59528</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52179</t>
+          <t>46171</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>80544</t>
+          <t>73643</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>167</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>113304</t>
+          <t>132844</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>96021</t>
+          <t>113299</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>134031</t>
+          <t>153988</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>11,83%</t>
         </is>
       </c>
     </row>
@@ -2205,107 +2205,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>842</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>602974</t>
+          <t>611755</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>589931</t>
+          <t>594838</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>614786</t>
+          <t>624783</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>839</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>677547</t>
+          <t>556785</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>662267</t>
+          <t>542670</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>690632</t>
+          <t>570142</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1681</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1280521</t>
+          <t>1168540</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1259794</t>
+          <t>1147396</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1297804</t>
+          <t>1188085</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>91,29%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>937</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>685072</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>685072</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>685072</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>911</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>651014</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>651014</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>651014</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>937</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>742811</t>
+          <t>616313</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>742811</t>
+          <t>616313</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>742811</t>
+          <t>616313</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1393825</t>
+          <t>1301384</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1393825</t>
+          <t>1301384</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1393825</t>
+          <t>1301384</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
